--- a/data/seed/portfolio/L-2025-3111/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-3111/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,33 +558,33 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>18566000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>9440000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Samarqand Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>225969710</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000116009222001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №229/26</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №2195 ОТ 01.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -600,39 +600,39 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>71581000</v>
+        <v>39543000</v>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>218463789</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000646943449001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7874</t>
+          <t>Оплата за упаковочные материалы, с/ф №8144</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -640,40 +640,40 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>8331000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>87531000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olmaliq Yog' Zavodi AJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>280695994</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000386366072001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9306 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №7034</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,31 +683,31 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>23188000</v>
+        <v>3613000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №199/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по дог. №129/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -724,31 +724,31 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>9826000</v>
+        <v>281960000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4948</t>
+          <t>Оплата за продукцию по дог. №27/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>9488000</v>
+        <v>7329000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №299/26 от 06.07.2026</t>
+          <t>Предоплата за товар по договору №113/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -806,31 +806,31 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>3753000</v>
+        <v>5283000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Angren Savdo MChJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>228106707</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000452391098001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №206/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №193/26 от 06.07.2026</t>
         </is>
       </c>
     </row>
@@ -845,35 +845,40 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>63099000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>5262000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Jizzax Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6973</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -881,40 +886,35 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>347533000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>63099000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Andijon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>289431495</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000166350791001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №283/26, НДС 12%</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -922,33 +922,33 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>4737000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>102385000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Navoiy Tur Servis MChJ</t>
+          <t>Bunyodkor Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>381259697</t>
+          <t>250500149</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000071160092001</t>
+          <t>20208000115303947001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №246/26 ОТ 07.07.2026</t>
+          <t>Оплата за товары согласно с/ф №3117</t>
         </is>
       </c>
     </row>
@@ -963,40 +963,40 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>10443000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>15898000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>204851284</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000530151970001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №219</t>
+          <t>Предоплата за товар по договору №174/26 от 07.07.2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1004,23 +1004,23 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>18810000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>4550000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Zarafshon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>327838192</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>20208000583762229001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1030,14 +1030,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №52/26 от 07.07.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №240/26 от 09.07.2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1046,39 +1046,39 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>38738000</v>
+        <v>6550000</v>
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Andijon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>212265638</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000560464933001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №23/26</t>
+          <t>АРЕНДНАЯ ПЛАТА ЗА ИЮЛЬ 2026 Г. ПО ДОГОВОРУ №30/22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1087,22 +1087,22 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>88328000</v>
+        <v>73509000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1112,14 +1112,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №234/26</t>
+          <t>Оплата за товары согласно счет-фактуре №8560</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,40 +1127,40 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>16234000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>42872000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo XK</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>332347257</t>
+          <t>205765423</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000371395715001</t>
+          <t>20208000354870771001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №180/26 от 08.07.2026</t>
+          <t>Предоплата за материалы по договору №232/26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1168,40 +1168,40 @@
           <t>115</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>6550000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>5133000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Qurilish XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>265450500</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000498115303001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №62/21</t>
+          <t>Оплата за продукцию по договору №162/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1209,40 +1209,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>9124000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>8604000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4307 за поставленный товар</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1251,39 +1251,39 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10312000</v>
+        <v>8604000</v>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №69/26 от 10.07.2026, НДС 12%</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,39 +1292,34 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>20180000</v>
+        <v>75200000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>300048512</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3111)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>16307000332664015417</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1491</t>
+          <t>Kredit shartnomasi L-2025-3111 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1334,21 +1329,21 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>12239000</v>
+        <v>11959000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>325278381</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000275837622001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1358,14 +1353,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Shartnoma №96/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №9582 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1375,38 +1370,38 @@
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>5157000</v>
+        <v>3818000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №122/26 ОТ 13.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №9040 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1414,40 +1409,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>11722000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>26291000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Navoiy Mebel AJ</t>
+          <t>Oqtosh Agro Servis XK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>215384006</t>
+          <t>343149501</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000881356806001</t>
+          <t>20208000635079197001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №6815</t>
+          <t>Оплата по счет-фактуре №7321 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1456,39 +1451,39 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>19877000</v>
+        <v>36763000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Xiva Tekstil MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>338400668</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000135680645001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №23/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №293/26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1497,39 +1492,39 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46845000</v>
+        <v>11070000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4047</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1538,39 +1533,39 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>203129000</v>
+        <v>22118000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4416</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTOMA №163/26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1578,40 +1573,40 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>22402000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>140020000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4786 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплаа за товары согласно с/ф №6472</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1621,38 +1616,38 @@
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>4255000</v>
+        <v>17677000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Navoiy Tur Servis MChJ</t>
+          <t>Ilhom Plastik MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>381259697</t>
+          <t>310670754</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000071160092001</t>
+          <t>20208000239109877001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9347 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №219/26 от 23.07.2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1660,40 +1655,40 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>8604000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>37577000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Samarqand Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>225969710</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000116009222001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Оплата за товар по счет-фактуре №4638 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,40 +1696,40 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>8604000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>22048000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Оплата за продукцию по договору 124/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1742,35 +1737,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>75200000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>16232000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3111)</t>
+          <t>Jizzax Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16307000332664015417</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3111 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №279/26 ОТ 24.07.2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1778,40 +1778,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>6468000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>4094000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000523532733001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5390 ОТ 17.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1821,38 +1821,38 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>4015000</v>
+        <v>18395000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Angren Savdo MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>228106707</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000452391098001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №244/26 от 17.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №6701 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1860,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>12378000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>10338000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lazzat Polimer AJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>324057654</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000363548707001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №5/26 ОТ 20.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №193/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1901,40 +1901,40 @@
           <t>133</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>25729000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>393786000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2407</t>
+          <t>Предоплата за товар по договору №273/26 от 28.07.2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1943,39 +1943,39 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>30122000</v>
+        <v>217478000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Xiva Tekstil MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>338400668</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000135680645001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2594</t>
+          <t>Оплата за транспортные услуги по договору №281/26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,38 +1985,38 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>15601000</v>
+        <v>12002000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №251 от 21.07.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №143/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2026,38 +2026,38 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>6570000</v>
+        <v>4645000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №50/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №148/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2067,38 +2067,38 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>6522000</v>
+        <v>5383000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4186 22.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №8/26 от 31.07.2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2108,21 +2108,21 @@
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>4644000</v>
+        <v>3873000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Olmaliq Yog' Zavodi AJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>280695994</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000386366072001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3741 за поставленный товар</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №150/26 ОТ 31.07.2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,35 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>3418000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Andijon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>289431495</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000166350791001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №271/26 от 23.07.2026</t>
+          <t>КОМИССИЯ БАНКА ЗА РАСЧЕТНО-КАССОВОЕ ОБСЛУЖИВАНИЕ ЗА ИЮЛЬ</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2189,39 +2184,39 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>10465000</v>
+        <v>26188000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Оплата за сырье по договору №93/26 от 04.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,40 +2224,35 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>4530000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>63672000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Navoiy Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>381259697</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000071160092001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №229/26 от 24.07.2026</t>
+          <t>ISH HAQI TO'LOVI IYUL 2026 (PLASTIK KARTALARGA)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>06.08.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2270,23 +2260,23 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>15683000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>14957000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Zarafshon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>327838192</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>20208000583762229001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2296,14 +2286,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №253/26</t>
+          <t>Оплата за товар по с/ф №3640 от 06.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2311,40 +2301,40 @@
           <t>143</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>248839000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>6609000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angren Savdo MChJ</t>
+          <t>Andijon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>228106707</t>
+          <t>212265638</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000452391098001</t>
+          <t>20208000560464933001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1046 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Арендная плата за август 2026 г. по договору №30/22</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2352,40 +2342,40 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>4094000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>286899000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Termiz Moy MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>234725733</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000476151122001</t>
+          <t>20208000139571596001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за продукцию по дог. №209/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2393,40 +2383,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>23683000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>11441000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Shahrisabz Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>286429948</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000622892028001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №258/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №44/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2435,22 +2425,22 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>27326000</v>
+        <v>47708000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,14 +2450,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №3360</t>
+          <t>Оплата за товары согласно счет-фактуре №8190</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2475,40 +2465,40 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>19458000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>571757000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Denov Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>205765423</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000354870771001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №9185 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товары согласно счет-фактуре №5501</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2518,38 +2508,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>11375000</v>
+        <v>58568000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1459</t>
+          <t>ОПЛАТА ПО С/Ф №2314 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2559,38 +2549,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>33163000</v>
+        <v>32637000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olmaliq Yog' Zavodi AJ</t>
+          <t>Samarqand Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>280695994</t>
+          <t>225969710</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000386366072001</t>
+          <t>20208000116009222001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплаа по счет-фактуре №4131 за поставленный товар</t>
+          <t>Предоплата за товар по договору №98/26 от 13.08.2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2600,21 +2590,21 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>10592000</v>
+        <v>13939000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Durdona Savdo MChJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>325278381</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000275837622001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2624,14 +2614,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №210/26 ОТ 29.07.2026</t>
+          <t>Оплата за продукцию по дог. №86/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2641,38 +2631,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>5932000</v>
+        <v>9868000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №82/26 от 29.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №220/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2680,40 +2670,40 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>4100000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>11114000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Andijon Mehmonxona MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>289431495</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000166350791001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9104 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №4769</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>15.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2721,40 +2711,35 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>10554000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>75200000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>390293072</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3111)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>16307000332664015417</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8230 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-3111 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2762,40 +2747,40 @@
           <t>154</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>12761000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>89548000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №178/26</t>
+          <t>Оплата за продукцию по договору №105/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2804,34 +2789,39 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>300000</v>
+        <v>8683000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2840,39 +2830,39 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>18235000</v>
+        <v>8683000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yangi Hayot Dori-Darmon XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>376033924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000820478591001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №22/26, QQS bilan</t>
+          <t>Jismoniy shaxslar daomad solig'i iyul 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2881,39 +2871,39 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>19536000</v>
+        <v>10470000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Navoiy Mebel AJ</t>
+          <t>Bunyodkor Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>215384006</t>
+          <t>250500149</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000881356806001</t>
+          <t>20208000115303947001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №141/26</t>
+          <t>Оплата за товары согласно счет-фактуре №4998</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2923,38 +2913,38 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>22861000</v>
+        <v>15049000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №141/26 от 03.08.2026</t>
+          <t>Оплата за товар по с/ф №3202 от 18.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2964,38 +2954,38 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>19397000</v>
+        <v>31129000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Angren Savdo MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>228106707</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000452391098001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Shartnoma №271/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3313 19.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3005,38 +2995,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>8492000</v>
+        <v>11000000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №955 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №242/26 от 19.08.2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3045,39 +3035,39 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>12257000</v>
+        <v>17671000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №142/26</t>
+          <t>Оплата за транспортные услуги по дог. №19/26</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3085,23 +3075,23 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>17845000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>20437000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3111,14 +3101,14 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №249/26</t>
+          <t>Оплата за продукцию по договору №196/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3126,40 +3116,40 @@
           <t>163</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>49375000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>15229000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Afrosiyob Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>204851284</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>20208000530151970001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф 7458</t>
+          <t>Оплата за продукцию по дог. №249/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3168,39 +3158,39 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>49686000</v>
+        <v>4131000</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Yangi Hayot Dori-Darmon XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>376033924</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000820478591001</t>
+          <t>20208000523532733001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за материлы по дог. №19/26</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3208,40 +3198,40 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>4630000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>11343000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №57/26, НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3250,39 +3240,39 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>15046000</v>
+        <v>16148000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Termiz Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>303392498</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000047859164001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №88/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №171/26</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3291,39 +3281,39 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>44975000</v>
+        <v>10735000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2961</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №5321</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3331,40 +3321,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>82581000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>325214000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Navoiy Mebel AJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>215384006</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000881356806001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7542</t>
+          <t>Оплата за продукцию по дог. №71/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3374,38 +3364,38 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>81065000</v>
+        <v>9318000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №146/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4389</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3413,40 +3403,35 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>9537000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>390293072</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6544 за поставленный товар</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3455,17 +3440,22 @@
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>63672000</v>
+        <v>22308000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Xiva Tekstil MChJ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>338400668</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000135680645001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3475,14 +3465,14 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №6045</t>
+          <t>Оплата за сырье по договору №214/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3492,38 +3482,38 @@
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>4921000</v>
+        <v>9523000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Olmaliq Yog' Zavodi AJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>280695994</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000386366072001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4219 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №67/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3533,38 +3523,38 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>33386000</v>
+        <v>3482000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7203 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №2985 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3572,40 +3562,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>6609000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>21779000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Qurilish XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>265450500</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000498115303001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №62/21</t>
+          <t>Оплата за продукцию по договору №3/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3615,38 +3605,38 @@
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>18023000</v>
+        <v>1374000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №261/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №1516 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3656,38 +3646,38 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>8708000</v>
+        <v>1848000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №265/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №147/26 от 04.09.2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3695,40 +3685,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>17631000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>7297000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Xiva Savdo MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>364081474</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000681054757001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №203/26</t>
+          <t>Оплата по счет-фактуре №5417 за поставленный овар</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3736,40 +3726,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>41956000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>1392000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Termiz Moy MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>234725733</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000139571596001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5255</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №273/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3777,40 +3767,35 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>94475000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>62097000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>390293072</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №213/26 от 13.08.2026</t>
+          <t>Avgust oyi uchun ish haqi, reestr №8755</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3818,40 +3803,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>90916000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>135273000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Xiva Tekstil MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>338400668</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000135680645001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №89/26 от 13.08.2026</t>
+          <t>Оплата за упаковочные материалы, сф №7972</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3861,38 +3846,38 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>52792000</v>
+        <v>136165000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7529 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №466 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3902,38 +3887,38 @@
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>7047000</v>
+        <v>2070000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Преоплата за товар по договору №128/26 от 14.08.2026</t>
+          <t>Предоплата за товар по договору №116/26 от 08.09.2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3942,39 +3927,39 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>8683000</v>
+        <v>56048000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Xiva Tekstil MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>338400668</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000135680645001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Оплата за сырье по договору №59/26 от 08.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3982,40 +3967,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>8683000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>16564000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Оплата за товар по счет-фактуре №6950 от 09.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>15.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4023,35 +4008,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>75200000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>4001000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3111)</t>
+          <t>Jizzax Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>16307000332664015417</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3111 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за товар по счет-фактуре №1197 от 09.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4061,38 +4051,38 @@
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>21239000</v>
+        <v>2717000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7692</t>
+          <t>Предоплата за товар по договору №77/26 от 09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4100,40 +4090,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>8713000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>6446000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Andijon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>212265638</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000560464933001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Shartnoma №91/26 bo'yicha oldindan to'lov</t>
+          <t>Аренда помещения за ентябрь, дог. №30/22</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4141,40 +4131,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>4957000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>66141000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №58/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №6744</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,40 +4172,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>11851000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>2670000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №192/26</t>
+          <t>Оплата по счет-фактуре №1203 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,23 +4213,23 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>14077000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>563257000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toshkent Dori-Darmon XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>349885274</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000288451493001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4249,14 +4239,14 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №5429</t>
+          <t>Оплата за продукцию по дог. №262/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4266,38 +4256,38 @@
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>62369000</v>
+        <v>7291000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2067 18.08.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6652 ОТ 14.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4307,38 +4297,38 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>9518000</v>
+        <v>4136000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Samarqand Sut Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>225969710</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000116009222001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4727 18.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №143/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4347,39 +4337,39 @@
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>18966000</v>
+        <v>8468000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>305505848</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000782050678001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2223</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4388,39 +4378,39 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>24971000</v>
+        <v>8468000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2637</t>
+          <t>НДФЛ за август 2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4428,23 +4418,23 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>11181000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>16437000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4454,14 +4444,14 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №33/26</t>
+          <t>Shartnoma №124/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4469,40 +4459,35 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>11779000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>75200000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Olmaliq Yog' Zavodi AJ</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>280695994</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3111)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000386366072001</t>
+          <t>16307000332664015417</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7445 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-3111 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4510,40 +4495,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>6507000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>94490000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №281/26 от 20.08.2026</t>
+          <t>Оплата за транспортные услуги по дог. №260/26</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4551,40 +4536,40 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>162304000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>2133000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №157/26</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №4302 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4594,38 +4579,38 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>6584000</v>
+        <v>1972000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Andijon Mehmonxona MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>289431495</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000166350791001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1256 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №63/26 от 16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4633,40 +4618,40 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>47108000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>7831000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Xiva Savdo MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>364081474</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000681054757001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №3158</t>
+          <t>Оплата по с/ф №6458 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4676,21 +4661,21 @@
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>260262000</v>
+        <v>2565000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>332347257</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000371395715001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4700,14 +4685,14 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4284 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5859 21.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4716,39 +4701,39 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>4131000</v>
+        <v>10597000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000476151122001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>НДС за агуст 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4757,39 +4742,39 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>11375000</v>
+        <v>41093000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Оплата за товары согласно счет-фактуре №7339</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4797,40 +4782,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>10490000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>45191000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Xiva Tekstil MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>338400668</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000135680645001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №296/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №6294</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4838,40 +4823,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>20678000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>4271000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>218463789</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000646943449001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №8/26</t>
+          <t>Оплата за товар по счет-фактуре №1816 от 22.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4879,40 +4864,40 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>21201000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>3155000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №57/26 от 25.08.2026, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6335 от 22.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4922,38 +4907,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>5541000</v>
+        <v>2262000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №706 от 26.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №3425 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4961,40 +4946,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>29111000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>26243000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №293/26 ОТ 26.08.2026, НДС 12%</t>
+          <t>Shartnoma №122/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5004,38 +4989,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>21570000</v>
+        <v>6585000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №185/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7175</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5045,38 +5030,38 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>21856000</v>
+        <v>4228000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1913 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №90/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5086,38 +5071,38 @@
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>12418000</v>
+        <v>3394000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6242</t>
+          <t>Предоплат за товар по договору №206/26 от 24.09.2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5127,21 +5112,21 @@
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>10254000</v>
+        <v>2686000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Olmaliq Yog' Zavodi AJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>280695994</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000386366072001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5151,14 +5136,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2908 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №7766 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5166,40 +5151,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>9256000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>129558000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Angren Savdo MChJ</t>
+          <t>Kamalak Logistik MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>228106707</t>
+          <t>346378926</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000452391098001</t>
+          <t>20208000694344975001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2678 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №9704</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5209,21 +5194,21 @@
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>8323000</v>
+        <v>6702000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Toshkent Avto Savdo XK</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>332347257</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000371395715001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5233,14 +5218,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2668</t>
+          <t>Оплата по счет-фактуре №9462 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5248,35 +5233,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>2245000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Jizzax Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата по счет-фактуре №7016 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5284,40 +5274,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>10581000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>1857000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Jizzax Qog'oz AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>300048512</t>
+          <t>229307251</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>20208000474099288001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №275/26, QQS bilan</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2656 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5325,40 +5315,40 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>13156000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>1492000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Navoiy Mebel AJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>215384006</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000881356806001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8025</t>
+          <t>Оплата за продукцию по договору №109/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5368,38 +5358,38 @@
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>32546000</v>
+        <v>1422000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Navoiy Tur Servis MChJ</t>
+          <t>Angren Metall Servis AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>381259697</t>
+          <t>269599433</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000071160092001</t>
+          <t>20208000636607265001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8995 03.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №210/26 от 28.09.2026</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5407,40 +5397,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>24779000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>4029000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>390293072</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000134740992001</t>
+          <t>20208000523532733001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №36/26 от 03.09.2026</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5449,39 +5439,34 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>39601000</v>
+        <v>300000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>300048512</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000435301519001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5394</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5489,1971 +5474,59 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>59241000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>165712000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Andijon Mehmonxona MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>289431495</t>
+          <t>350584877</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000166350791001</t>
+          <t>20208000205067807001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8911 за поставленный товар</t>
+          <t>Оплата за упаковочные материалы, с/ф №8457</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>23152000</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Shartnoma №137/26 bo'yicha oldindan to'lov</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="n">
+        <v>2761571000</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>2750771000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>18771000</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №9847 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>07.09.2026</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v>10370000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>300048512</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>20208000435301519001</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по дог. №18/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>07.09.2026</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>62097000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Yangi Asr Bank</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>09.09.2026</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>126020000</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №160/26 от 09.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>09.09.2026</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>6446000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Oltin Vodiy Qurilish XK</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>265450500</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>20208000498115303001</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Арендная плата за сентябрь 2026 г. по договору №62/21</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>09.09.2026</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>11883000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>300048512</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>20208000435301519001</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по дог. №119/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>11061000</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №133/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>36576000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Navoiy Mebel AJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>215384006</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>20208000881356806001</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по дог. №283/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>11.09.2026</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>7820000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>218463789</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>20208000646943449001</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №7149</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>11.09.2026</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>167322000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Farovon Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>305505848</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>20208000782050678001</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по дог. №296/26 от 11.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>50869000</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №118/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>45821000</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Andijon Mehmonxona MChJ</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>289431495</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>20208000166350791001</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №122/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>9295000</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Shartnoma №134/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>14.09.2026</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>8219000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>300048512</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>20208000435301519001</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartn. №246/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>11284000</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №274/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>15.09.2026</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>75200000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3111)</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>16307000332664015417</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2025-3111 bo'yicha navbatdagi to'lov (09.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>94476000</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3178</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>8468000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Социальный налог за август 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>8468000</v>
-      </c>
-      <c r="D151" s="2" t="n"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>16.09.2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>52416000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>300048512</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000435301519001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №289/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>8337000</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>332347257</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000371395715001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №3991 от 17.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>4660000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Farovon Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>305505848</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000782050678001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №7822</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>17.09.2026</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>12006000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>300048512</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000435301519001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №282/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>10835000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Xiva Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>364081474</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000681054757001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №134/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>64111000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №870 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>10636000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>332347257</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000371395715001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>8603000</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>332347257</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000371395715001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №5768 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>10522000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>НДС за август 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>21.09.2026</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>17719000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>300048512</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000435301519001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №227/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>10250000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4418 22.09.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>22.09.2026</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>8806000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №3304 от 22.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>14732000</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №105/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>23.09.2026</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>9797000</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №189/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>8367000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Olmaliq Yog' Zavodi AJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>280695994</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000386366072001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №120/26 от 24.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>24.09.2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>4029000</v>
-      </c>
-      <c r="D167" s="2" t="n"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000476151122001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию согласно счету</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n">
-        <v>116366000</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №100/26 от 28.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n">
-        <v>49625000</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer XK</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>390293072</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000134740992001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №90/26 от 28.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n">
-        <v>8274000</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Angren Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>228106707</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000452391098001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №6286 за поставленный товар</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>4659000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Farovon Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>305505848</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000782050678001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №9267</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>8017000</v>
-      </c>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>300048512</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000435301519001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №69/26 от 28.09.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v>10659000</v>
-      </c>
-      <c r="D173" s="2" t="n"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Toshkent Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>349885274</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000288451493001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №8235</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>20840000</v>
-      </c>
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Guliston Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>300048512</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000435301519001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №214/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>287422000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Zarafshon Avto Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>218463789</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000646943449001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №4040</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>51627000</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Toshkent Avto Savdo XK</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>332347257</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000371395715001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №226/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Yangi Asr Bank</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Bank xizmati uchun komissiya</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>4936000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Xiva Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>364081474</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000681054757001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №59/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="n">
-        <v>2707580000</v>
-      </c>
-      <c r="D179" s="4" t="n">
-        <v>2696780000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C180" s="4" t="n">
+      <c r="C133" s="4" t="n">
         <v>216200000</v>
       </c>
-      <c r="D180" s="4" t="n"/>
+      <c r="D133" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
